--- a/public/templates/godrej-sfdc-template.xlsx
+++ b/public/templates/godrej-sfdc-template.xlsx
@@ -3,9 +3,39 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Godrej SFDC" sheetId="1" r:id="rId1"/>
+    <sheet name="Godrej SFDC Data" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>SalesDost</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <t>Required. The Plan ID for the Godrej SFDC record.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>Required. Customer mobile phone number.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <t>Required. The Contract Booking ID.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <t>Optional. Customer full name.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,7 +427,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D5"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,32 +445,70 @@
       <c r="C1" t="str">
         <v>ContractBookingID</v>
       </c>
+      <c r="D1" t="str">
+        <v>Customer Name</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>P12345</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>9876543210</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>C001</v>
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>P67890</v>
+        <v>PLN-001</v>
       </c>
       <c r="B3" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="C3" t="str">
+        <v>CTR-20240001</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Ramesh Kumar</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PLN-002</v>
+      </c>
+      <c r="B4" t="str">
         <v>9123456789</v>
       </c>
-      <c r="C3" t="str">
-        <v>C002</v>
+      <c r="C4" t="str">
+        <v>CTR-20240002</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Sunita Sharma</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PLN-003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>8800112233</v>
+      </c>
+      <c r="C5" t="str">
+        <v>CTR-20240003</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>